--- a/output/laminas_comunales/comunal_s_isapre_a_2021_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2021_metropolitana.xlsx
@@ -375,571 +375,571 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C2">
-        <v>197067</v>
+        <v>81.38481449525453</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C3">
-        <v>150122</v>
+        <v>69.72096330810788</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="C4">
-        <v>125057</v>
+        <v>64.66100323055159</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C5">
-        <v>118427</v>
+        <v>63.04360866174795</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="C6">
-        <v>102406</v>
+        <v>54.07971285835625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="C7">
-        <v>96638</v>
+        <v>52.22647368712915</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Providencia</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="C8">
-        <v>91871</v>
+        <v>36.65384836962784</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="C9">
-        <v>64141</v>
+        <v>35.00475499274238</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="C10">
-        <v>63060</v>
+        <v>34.00450521656655</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="C11">
-        <v>56295</v>
+        <v>27.95010785554521</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="C12">
-        <v>51627</v>
+        <v>26.09482251157064</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="C13">
-        <v>50899</v>
+        <v>24.7577812884808</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>La Reina</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C14">
-        <v>47090</v>
+        <v>24.74023266583497</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>Lampa</t>
         </is>
       </c>
       <c r="C15">
-        <v>43988</v>
+        <v>24.05737815216514</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="C16">
-        <v>43758</v>
+        <v>23.51700225582756</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="C17">
-        <v>40803</v>
+        <v>22.28180412540711</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Macul</t>
+          <t>Calera de Tango</t>
         </is>
       </c>
       <c r="C18">
-        <v>35114</v>
+        <v>21.66949071261869</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="C19">
-        <v>34968</v>
+        <v>21.19209126647653</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lampa</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="C20">
-        <v>26817</v>
+        <v>20.6372579094832</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Estación Central</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="C21">
-        <v>26373</v>
+        <v>19.71147918293535</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="C22">
-        <v>22277</v>
+        <v>19.64454649827784</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="C23">
-        <v>21388</v>
+        <v>18.42637668331542</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="C24">
-        <v>20182</v>
+        <v>18.25451434071909</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
+          <t>San José de Maipo</t>
         </is>
       </c>
       <c r="C25">
-        <v>19695</v>
+        <v>17.85433733587701</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="C26">
-        <v>17255</v>
+        <v>17.68396666559413</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>Cerrillos</t>
         </is>
       </c>
       <c r="C27">
-        <v>17163</v>
+        <v>17.29839300542178</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="C28">
-        <v>16488</v>
+        <v>16.89534821761603</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Conchalí</t>
+          <t>Alhué</t>
         </is>
       </c>
       <c r="C29">
-        <v>15736</v>
+        <v>15.34684627974317</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>El Bosque</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="C30">
-        <v>14932</v>
+        <v>15.16936332733223</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>Quinta Normal</t>
         </is>
       </c>
       <c r="C31">
-        <v>14388</v>
+        <v>15.13253937764118</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="C32">
-        <v>14166</v>
+        <v>14.66413978311861</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="C33">
-        <v>14129</v>
+        <v>14.64531351975501</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="C34">
-        <v>12835</v>
+        <v>13.87740268924401</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Curacaví</t>
         </is>
       </c>
       <c r="C35">
-        <v>12683</v>
+        <v>13.58619305639173</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
+          <t>Isla de Maipo</t>
         </is>
       </c>
       <c r="C36">
-        <v>10765</v>
+        <v>13.49290635296681</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>La Granja</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="C37">
-        <v>10418</v>
+        <v>13.07435426411639</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
+          <t>Conchalí</t>
         </is>
       </c>
       <c r="C38">
-        <v>10240</v>
+        <v>12.01652501279085</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>Renca</t>
         </is>
       </c>
       <c r="C39">
-        <v>9931</v>
+        <v>11.61443565468658</v>
       </c>
     </row>
     <row r="40">
@@ -954,187 +954,187 @@
         </is>
       </c>
       <c r="C40">
-        <v>8607</v>
+        <v>11.611623765582</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>La Pintana</t>
+          <t>Lo Prado</t>
         </is>
       </c>
       <c r="C41">
-        <v>8488</v>
+        <v>10.51367085228498</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
+          <t>Pedro Aguirre Cerda</t>
         </is>
       </c>
       <c r="C42">
-        <v>6895</v>
+        <v>10.32445548447735</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
+          <t>El Bosque</t>
         </is>
       </c>
       <c r="C43">
-        <v>6778</v>
+        <v>9.201266930405097</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="C44">
-        <v>6773</v>
+        <v>9.16131334760885</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>María Pinto</t>
         </is>
       </c>
       <c r="C45">
-        <v>6578</v>
+        <v>8.841523583974739</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
+          <t>El Monte</t>
         </is>
       </c>
       <c r="C46">
-        <v>4955</v>
+        <v>8.714064020621269</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>La Granja</t>
         </is>
       </c>
       <c r="C47">
-        <v>4739</v>
+        <v>8.691154510340455</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>El Monte</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="C48">
-        <v>3313</v>
+        <v>7.547472893121451</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
+          <t>Cerro Navia</t>
         </is>
       </c>
       <c r="C49">
-        <v>3182</v>
+        <v>7.139057423009461</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>María Pinto</t>
+          <t>Lo Espejo</t>
         </is>
       </c>
       <c r="C50">
-        <v>1344</v>
+        <v>6.860969590829486</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alhué</t>
+          <t>San Pedro</t>
         </is>
       </c>
       <c r="C51">
-        <v>1219</v>
+        <v>5.689053193674265</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>San Pedro</t>
+          <t>La Pintana</t>
         </is>
       </c>
       <c r="C52">
-        <v>554</v>
+        <v>4.783912347543793</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
